--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,6 +2233,1790 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120308189</v>
+      </c>
+      <c r="B15" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>702314</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359093</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120308180</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97885</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>702288</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6359071</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120308206</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97882</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>702378</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6359096</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120308207</v>
+      </c>
+      <c r="B18" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>702378</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6359096</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120308197</v>
+      </c>
+      <c r="B19" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>702363</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359087</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120308216</v>
+      </c>
+      <c r="B20" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>702411</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6359095</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120308202</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97882</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>702373</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6359092</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120308211</v>
+      </c>
+      <c r="B22" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>702376</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6359086</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120308200</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>702373</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6359092</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120308178</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97885</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>702283</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6359063</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120308184</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>702300</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6359068</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120308166</v>
+      </c>
+      <c r="B26" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>702247</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6359023</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120308195</v>
+      </c>
+      <c r="B27" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>702354</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6359099</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120308186</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108787</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>702315</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6359085</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120308191</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97882</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>702314</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6359093</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120308199</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97882</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>702363</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6359087</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308189</v>
+        <v>120308195</v>
       </c>
       <c r="B15" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702314</v>
+        <v>702354</v>
       </c>
       <c r="R15" t="n">
-        <v>6359093</v>
+        <v>6359099</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308180</v>
+        <v>120308186</v>
       </c>
       <c r="B16" t="n">
-        <v>97885</v>
+        <v>108811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,50 +2354,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702288</v>
+        <v>702315</v>
       </c>
       <c r="R16" t="n">
-        <v>6359071</v>
+        <v>6359085</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2458,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308206</v>
+        <v>120308189</v>
       </c>
       <c r="B17" t="n">
-        <v>97882</v>
+        <v>108811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,47 +2461,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702378</v>
+        <v>702314</v>
       </c>
       <c r="R17" t="n">
-        <v>6359096</v>
+        <v>6359093</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2574,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308207</v>
+        <v>120308211</v>
       </c>
       <c r="B18" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2609,7 +2591,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2623,10 +2605,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702378</v>
+        <v>702376</v>
       </c>
       <c r="R18" t="n">
-        <v>6359096</v>
+        <v>6359086</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2690,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308197</v>
+        <v>120308200</v>
       </c>
       <c r="B19" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2730,13 +2712,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702363</v>
+        <v>702373</v>
       </c>
       <c r="R19" t="n">
-        <v>6359087</v>
+        <v>6359092</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2800,7 +2782,7 @@
         <v>120308216</v>
       </c>
       <c r="B20" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308202</v>
+        <v>120308191</v>
       </c>
       <c r="B21" t="n">
-        <v>97882</v>
+        <v>97905</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2939,7 +2921,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2953,10 +2935,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702373</v>
+        <v>702314</v>
       </c>
       <c r="R21" t="n">
-        <v>6359092</v>
+        <v>6359093</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3020,10 +3002,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308211</v>
+        <v>120308206</v>
       </c>
       <c r="B22" t="n">
-        <v>108787</v>
+        <v>97905</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,30 +3014,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3069,10 +3051,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702376</v>
+        <v>702378</v>
       </c>
       <c r="R22" t="n">
-        <v>6359086</v>
+        <v>6359096</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3136,10 +3118,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308200</v>
+        <v>120308199</v>
       </c>
       <c r="B23" t="n">
-        <v>108787</v>
+        <v>97905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,41 +3130,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702373</v>
+        <v>702363</v>
       </c>
       <c r="R23" t="n">
-        <v>6359092</v>
+        <v>6359087</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3246,7 +3237,7 @@
         <v>120308178</v>
       </c>
       <c r="B24" t="n">
-        <v>97885</v>
+        <v>97908</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3359,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308184</v>
+        <v>120308180</v>
       </c>
       <c r="B25" t="n">
-        <v>108787</v>
+        <v>97908</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3371,41 +3362,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702300</v>
+        <v>702288</v>
       </c>
       <c r="R25" t="n">
-        <v>6359068</v>
+        <v>6359071</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308166</v>
+        <v>120308202</v>
       </c>
       <c r="B26" t="n">
-        <v>108787</v>
+        <v>97905</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,41 +3478,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702247</v>
+        <v>702373</v>
       </c>
       <c r="R26" t="n">
-        <v>6359023</v>
+        <v>6359092</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3573,10 +3582,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308195</v>
+        <v>120308197</v>
       </c>
       <c r="B27" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,13 +3622,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702354</v>
+        <v>702363</v>
       </c>
       <c r="R27" t="n">
-        <v>6359099</v>
+        <v>6359087</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3680,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308186</v>
+        <v>120308166</v>
       </c>
       <c r="B28" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3720,13 +3729,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702315</v>
+        <v>702247</v>
       </c>
       <c r="R28" t="n">
-        <v>6359085</v>
+        <v>6359023</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3787,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308191</v>
+        <v>120308207</v>
       </c>
       <c r="B29" t="n">
-        <v>97882</v>
+        <v>108811</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3799,30 +3808,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3836,10 +3845,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702314</v>
+        <v>702378</v>
       </c>
       <c r="R29" t="n">
-        <v>6359093</v>
+        <v>6359096</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3903,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308199</v>
+        <v>120308184</v>
       </c>
       <c r="B30" t="n">
-        <v>97882</v>
+        <v>108811</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3915,47 +3924,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702363</v>
+        <v>702300</v>
       </c>
       <c r="R30" t="n">
-        <v>6359087</v>
+        <v>6359068</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,7 +2235,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308195</v>
+        <v>120308211</v>
       </c>
       <c r="B15" t="n">
         <v>108811</v>
@@ -2268,17 +2268,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702354</v>
+        <v>702376</v>
       </c>
       <c r="R15" t="n">
-        <v>6359099</v>
+        <v>6359086</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2342,7 +2351,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308186</v>
+        <v>120308216</v>
       </c>
       <c r="B16" t="n">
         <v>108811</v>
@@ -2382,10 +2391,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702315</v>
+        <v>702411</v>
       </c>
       <c r="R16" t="n">
-        <v>6359085</v>
+        <v>6359095</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2449,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308189</v>
+        <v>120308180</v>
       </c>
       <c r="B17" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,41 +2470,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702314</v>
+        <v>702288</v>
       </c>
       <c r="R17" t="n">
-        <v>6359093</v>
+        <v>6359071</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2556,7 +2574,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308211</v>
+        <v>120308207</v>
       </c>
       <c r="B18" t="n">
         <v>108811</v>
@@ -2591,7 +2609,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2605,10 +2623,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702376</v>
+        <v>702378</v>
       </c>
       <c r="R18" t="n">
-        <v>6359086</v>
+        <v>6359096</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2672,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308200</v>
+        <v>120308206</v>
       </c>
       <c r="B19" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,38 +2702,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702373</v>
+        <v>702378</v>
       </c>
       <c r="R19" t="n">
-        <v>6359092</v>
+        <v>6359096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2779,7 +2806,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308216</v>
+        <v>120308184</v>
       </c>
       <c r="B20" t="n">
         <v>108811</v>
@@ -2819,13 +2846,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702411</v>
+        <v>702300</v>
       </c>
       <c r="R20" t="n">
-        <v>6359095</v>
+        <v>6359068</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2886,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308191</v>
+        <v>120308166</v>
       </c>
       <c r="B21" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,50 +2925,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702314</v>
+        <v>702247</v>
       </c>
       <c r="R21" t="n">
-        <v>6359093</v>
+        <v>6359023</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3002,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308206</v>
+        <v>120308178</v>
       </c>
       <c r="B22" t="n">
-        <v>97905</v>
+        <v>97908</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3018,26 +3036,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3051,10 +3069,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702378</v>
+        <v>702283</v>
       </c>
       <c r="R22" t="n">
-        <v>6359096</v>
+        <v>6359063</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3234,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308178</v>
+        <v>120308200</v>
       </c>
       <c r="B24" t="n">
-        <v>97908</v>
+        <v>108811</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3246,47 +3264,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702283</v>
+        <v>702373</v>
       </c>
       <c r="R24" t="n">
-        <v>6359063</v>
+        <v>6359092</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3350,10 +3359,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308180</v>
+        <v>120308189</v>
       </c>
       <c r="B25" t="n">
-        <v>97908</v>
+        <v>108811</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,50 +3371,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702288</v>
+        <v>702314</v>
       </c>
       <c r="R25" t="n">
-        <v>6359071</v>
+        <v>6359093</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308202</v>
+        <v>120308191</v>
       </c>
       <c r="B26" t="n">
         <v>97905</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702373</v>
+        <v>702314</v>
       </c>
       <c r="R26" t="n">
-        <v>6359092</v>
+        <v>6359093</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308166</v>
+        <v>120308202</v>
       </c>
       <c r="B28" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,41 +3701,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702247</v>
+        <v>702373</v>
       </c>
       <c r="R28" t="n">
-        <v>6359023</v>
+        <v>6359092</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3796,7 +3805,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308207</v>
+        <v>120308186</v>
       </c>
       <c r="B29" t="n">
         <v>108811</v>
@@ -3829,26 +3838,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702378</v>
+        <v>702315</v>
       </c>
       <c r="R29" t="n">
-        <v>6359096</v>
+        <v>6359085</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308184</v>
+        <v>120308195</v>
       </c>
       <c r="B30" t="n">
         <v>108811</v>
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702300</v>
+        <v>702354</v>
       </c>
       <c r="R30" t="n">
-        <v>6359068</v>
+        <v>6359099</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308207</v>
+        <v>120308206</v>
       </c>
       <c r="B18" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,30 +2586,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308206</v>
+        <v>120308207</v>
       </c>
       <c r="B19" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,30 +2702,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4017,6 +4017,960 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120419638</v>
+      </c>
+      <c r="B31" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>702258</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6358853</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120419636</v>
+      </c>
+      <c r="B32" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>449</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>702224</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6358856</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120419631</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90033</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rödbrun jordstjärna</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Geastrum rufescens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>702248</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6359026</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120419627</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>702369</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6359158</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120419634</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86396</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>473</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>702277</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6358938</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120419635</v>
+      </c>
+      <c r="B36" t="n">
+        <v>86486</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>702277</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6358938</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120419628</v>
+      </c>
+      <c r="B37" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>702321</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6359134</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120419637</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>702224</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6358856</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120419629</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87408</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>239233</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ekvaxskivling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hygrophorus cossus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Sowerby) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>702269</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6359044</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308211</v>
+        <v>120308180</v>
       </c>
       <c r="B15" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,30 +2247,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702376</v>
+        <v>702288</v>
       </c>
       <c r="R15" t="n">
-        <v>6359086</v>
+        <v>6359071</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308216</v>
+        <v>120308197</v>
       </c>
       <c r="B16" t="n">
         <v>108811</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702411</v>
+        <v>702363</v>
       </c>
       <c r="R16" t="n">
-        <v>6359095</v>
+        <v>6359087</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308180</v>
+        <v>120308191</v>
       </c>
       <c r="B17" t="n">
-        <v>97908</v>
+        <v>97905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,26 +2474,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702288</v>
+        <v>702314</v>
       </c>
       <c r="R17" t="n">
-        <v>6359071</v>
+        <v>6359093</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308206</v>
+        <v>120308207</v>
       </c>
       <c r="B18" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,30 +2586,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308207</v>
+        <v>120308206</v>
       </c>
       <c r="B19" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,30 +2702,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2806,7 +2806,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308184</v>
+        <v>120308195</v>
       </c>
       <c r="B20" t="n">
         <v>108811</v>
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702300</v>
+        <v>702354</v>
       </c>
       <c r="R20" t="n">
-        <v>6359068</v>
+        <v>6359099</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308166</v>
+        <v>120308178</v>
       </c>
       <c r="B21" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2925,41 +2925,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702247</v>
+        <v>702283</v>
       </c>
       <c r="R21" t="n">
-        <v>6359023</v>
+        <v>6359063</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3020,10 +3029,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308178</v>
+        <v>120308184</v>
       </c>
       <c r="B22" t="n">
-        <v>97908</v>
+        <v>108811</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,50 +3041,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702283</v>
+        <v>702300</v>
       </c>
       <c r="R22" t="n">
-        <v>6359063</v>
+        <v>6359068</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308199</v>
+        <v>120308166</v>
       </c>
       <c r="B23" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,47 +3148,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702363</v>
+        <v>702247</v>
       </c>
       <c r="R23" t="n">
-        <v>6359087</v>
+        <v>6359023</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308200</v>
+        <v>120308189</v>
       </c>
       <c r="B24" t="n">
         <v>108811</v>
@@ -3292,10 +3283,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702373</v>
+        <v>702314</v>
       </c>
       <c r="R24" t="n">
-        <v>6359092</v>
+        <v>6359093</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3359,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308189</v>
+        <v>120308202</v>
       </c>
       <c r="B25" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3371,38 +3362,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702314</v>
+        <v>702373</v>
       </c>
       <c r="R25" t="n">
-        <v>6359093</v>
+        <v>6359092</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308191</v>
+        <v>120308216</v>
       </c>
       <c r="B26" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,47 +3478,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702314</v>
+        <v>702411</v>
       </c>
       <c r="R26" t="n">
-        <v>6359093</v>
+        <v>6359095</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3582,7 +3573,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308197</v>
+        <v>120308186</v>
       </c>
       <c r="B27" t="n">
         <v>108811</v>
@@ -3622,13 +3613,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702363</v>
+        <v>702315</v>
       </c>
       <c r="R27" t="n">
-        <v>6359087</v>
+        <v>6359085</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3689,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308202</v>
+        <v>120308200</v>
       </c>
       <c r="B28" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,37 +3692,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
@@ -3805,7 +3787,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308186</v>
+        <v>120308211</v>
       </c>
       <c r="B29" t="n">
         <v>108811</v>
@@ -3838,17 +3820,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702315</v>
+        <v>702376</v>
       </c>
       <c r="R29" t="n">
-        <v>6359085</v>
+        <v>6359086</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3912,10 +3903,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308195</v>
+        <v>120308199</v>
       </c>
       <c r="B30" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3924,41 +3915,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702354</v>
+        <v>702363</v>
       </c>
       <c r="R30" t="n">
-        <v>6359099</v>
+        <v>6359087</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120419638</v>
+        <v>120419636</v>
       </c>
       <c r="B31" t="n">
-        <v>86282</v>
+        <v>86367</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702258</v>
+        <v>702224</v>
       </c>
       <c r="R31" t="n">
-        <v>6358853</v>
+        <v>6358856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120419636</v>
+        <v>120419637</v>
       </c>
       <c r="B32" t="n">
-        <v>86367</v>
+        <v>86373</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120419627</v>
+        <v>120419629</v>
       </c>
       <c r="B34" t="n">
-        <v>90600</v>
+        <v>87408</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,21 +4353,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>239233</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus cossus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Sowerby) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702369</v>
+        <v>702269</v>
       </c>
       <c r="R34" t="n">
-        <v>6359158</v>
+        <v>6359044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120419637</v>
+        <v>120419638</v>
       </c>
       <c r="B38" t="n">
-        <v>86373</v>
+        <v>86282</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4773,25 +4773,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702224</v>
+        <v>702258</v>
       </c>
       <c r="R38" t="n">
-        <v>6358856</v>
+        <v>6358853</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120419629</v>
+        <v>120419627</v>
       </c>
       <c r="B39" t="n">
-        <v>87408</v>
+        <v>90600</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4883,21 +4883,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>239233</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702269</v>
+        <v>702369</v>
       </c>
       <c r="R39" t="n">
-        <v>6359044</v>
+        <v>6359158</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308180</v>
+        <v>120308191</v>
       </c>
       <c r="B15" t="n">
-        <v>97908</v>
+        <v>97905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702288</v>
+        <v>702314</v>
       </c>
       <c r="R15" t="n">
-        <v>6359071</v>
+        <v>6359093</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308191</v>
+        <v>120308200</v>
       </c>
       <c r="B17" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,47 +2470,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702314</v>
+        <v>702373</v>
       </c>
       <c r="R17" t="n">
-        <v>6359093</v>
+        <v>6359092</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2574,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308207</v>
+        <v>120308206</v>
       </c>
       <c r="B18" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,30 +2577,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2690,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308206</v>
+        <v>120308166</v>
       </c>
       <c r="B19" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,50 +2693,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702378</v>
+        <v>702247</v>
       </c>
       <c r="R19" t="n">
-        <v>6359096</v>
+        <v>6359023</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2806,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308195</v>
+        <v>120308178</v>
       </c>
       <c r="B20" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2818,38 +2800,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702354</v>
+        <v>702283</v>
       </c>
       <c r="R20" t="n">
-        <v>6359099</v>
+        <v>6359063</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2913,10 +2904,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308178</v>
+        <v>120308195</v>
       </c>
       <c r="B21" t="n">
-        <v>97908</v>
+        <v>108811</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2925,47 +2916,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702283</v>
+        <v>702354</v>
       </c>
       <c r="R21" t="n">
-        <v>6359063</v>
+        <v>6359099</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3029,10 +3011,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308184</v>
+        <v>120308180</v>
       </c>
       <c r="B22" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3041,41 +3023,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702300</v>
+        <v>702288</v>
       </c>
       <c r="R22" t="n">
-        <v>6359068</v>
+        <v>6359071</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3136,7 +3127,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308166</v>
+        <v>120308207</v>
       </c>
       <c r="B23" t="n">
         <v>108811</v>
@@ -3169,20 +3160,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702247</v>
+        <v>702378</v>
       </c>
       <c r="R23" t="n">
-        <v>6359023</v>
+        <v>6359096</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308189</v>
+        <v>120308186</v>
       </c>
       <c r="B24" t="n">
         <v>108811</v>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702314</v>
+        <v>702315</v>
       </c>
       <c r="R24" t="n">
-        <v>6359093</v>
+        <v>6359085</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308202</v>
+        <v>120308216</v>
       </c>
       <c r="B25" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,47 +3362,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702373</v>
+        <v>702411</v>
       </c>
       <c r="R25" t="n">
-        <v>6359092</v>
+        <v>6359095</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3466,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308216</v>
+        <v>120308202</v>
       </c>
       <c r="B26" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,38 +3469,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702411</v>
+        <v>702373</v>
       </c>
       <c r="R26" t="n">
-        <v>6359095</v>
+        <v>6359092</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308186</v>
+        <v>120308184</v>
       </c>
       <c r="B27" t="n">
         <v>108811</v>
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702315</v>
+        <v>702300</v>
       </c>
       <c r="R27" t="n">
-        <v>6359085</v>
+        <v>6359068</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308200</v>
+        <v>120308199</v>
       </c>
       <c r="B28" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,41 +3692,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702373</v>
+        <v>702363</v>
       </c>
       <c r="R28" t="n">
-        <v>6359092</v>
+        <v>6359087</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3903,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308199</v>
+        <v>120308189</v>
       </c>
       <c r="B30" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3915,50 +3924,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702363</v>
+        <v>702314</v>
       </c>
       <c r="R30" t="n">
-        <v>6359087</v>
+        <v>6359093</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120419636</v>
+        <v>120419627</v>
       </c>
       <c r="B31" t="n">
-        <v>86367</v>
+        <v>90600</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>449</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702224</v>
+        <v>702369</v>
       </c>
       <c r="R31" t="n">
-        <v>6358856</v>
+        <v>6359158</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120419637</v>
+        <v>120419629</v>
       </c>
       <c r="B32" t="n">
-        <v>86373</v>
+        <v>87408</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4137,25 +4137,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>239233</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Ekvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hygrophorus cossus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Sowerby) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702224</v>
+        <v>702269</v>
       </c>
       <c r="R32" t="n">
-        <v>6358856</v>
+        <v>6359044</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120419631</v>
+        <v>120419638</v>
       </c>
       <c r="B33" t="n">
-        <v>90033</v>
+        <v>86282</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,21 +4247,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2009</v>
+        <v>3712</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702248</v>
+        <v>702258</v>
       </c>
       <c r="R33" t="n">
-        <v>6359026</v>
+        <v>6358853</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120419629</v>
+        <v>120419636</v>
       </c>
       <c r="B34" t="n">
-        <v>87408</v>
+        <v>86367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,25 +4349,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>239233</v>
+        <v>449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702269</v>
+        <v>702224</v>
       </c>
       <c r="R34" t="n">
-        <v>6359044</v>
+        <v>6358856</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120419634</v>
+        <v>120419628</v>
       </c>
       <c r="B35" t="n">
-        <v>86396</v>
+        <v>86449</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4459,21 +4459,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702277</v>
+        <v>702321</v>
       </c>
       <c r="R35" t="n">
-        <v>6358938</v>
+        <v>6359134</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120419635</v>
+        <v>120419637</v>
       </c>
       <c r="B36" t="n">
-        <v>86486</v>
+        <v>86373</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,21 +4565,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702277</v>
+        <v>702224</v>
       </c>
       <c r="R36" t="n">
-        <v>6358938</v>
+        <v>6358856</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120419628</v>
+        <v>120419635</v>
       </c>
       <c r="B37" t="n">
-        <v>86449</v>
+        <v>86486</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4667,25 +4667,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702321</v>
+        <v>702277</v>
       </c>
       <c r="R37" t="n">
-        <v>6359134</v>
+        <v>6358938</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120419638</v>
+        <v>120419634</v>
       </c>
       <c r="B38" t="n">
-        <v>86282</v>
+        <v>86396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4773,25 +4773,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3712</v>
+        <v>473</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702258</v>
+        <v>702277</v>
       </c>
       <c r="R38" t="n">
-        <v>6358853</v>
+        <v>6358938</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120419627</v>
+        <v>120419631</v>
       </c>
       <c r="B39" t="n">
-        <v>90600</v>
+        <v>90033</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>2009</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702369</v>
+        <v>702248</v>
       </c>
       <c r="R39" t="n">
-        <v>6359158</v>
+        <v>6359026</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308191</v>
+        <v>120308195</v>
       </c>
       <c r="B15" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,47 +2247,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702314</v>
+        <v>702354</v>
       </c>
       <c r="R15" t="n">
-        <v>6359093</v>
+        <v>6359099</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2351,10 +2342,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308197</v>
+        <v>120308199</v>
       </c>
       <c r="B16" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,28 +2354,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308200</v>
+        <v>120308178</v>
       </c>
       <c r="B17" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,38 +2470,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702373</v>
+        <v>702283</v>
       </c>
       <c r="R17" t="n">
-        <v>6359092</v>
+        <v>6359063</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2565,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308206</v>
+        <v>120308166</v>
       </c>
       <c r="B18" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2577,50 +2586,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702378</v>
+        <v>702247</v>
       </c>
       <c r="R18" t="n">
-        <v>6359096</v>
+        <v>6359023</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308166</v>
+        <v>120308216</v>
       </c>
       <c r="B19" t="n">
         <v>108811</v>
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702247</v>
+        <v>702411</v>
       </c>
       <c r="R19" t="n">
-        <v>6359023</v>
+        <v>6359095</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308178</v>
+        <v>120308202</v>
       </c>
       <c r="B20" t="n">
-        <v>97908</v>
+        <v>97905</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,26 +2804,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702283</v>
+        <v>702373</v>
       </c>
       <c r="R20" t="n">
-        <v>6359063</v>
+        <v>6359092</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308195</v>
+        <v>120308186</v>
       </c>
       <c r="B21" t="n">
         <v>108811</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702354</v>
+        <v>702315</v>
       </c>
       <c r="R21" t="n">
-        <v>6359099</v>
+        <v>6359085</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308180</v>
+        <v>120308191</v>
       </c>
       <c r="B22" t="n">
-        <v>97908</v>
+        <v>97905</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3027,26 +3027,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3060,13 +3060,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702288</v>
+        <v>702314</v>
       </c>
       <c r="R22" t="n">
-        <v>6359071</v>
+        <v>6359093</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308207</v>
+        <v>120308197</v>
       </c>
       <c r="B23" t="n">
         <v>108811</v>
@@ -3160,29 +3160,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702378</v>
+        <v>702363</v>
       </c>
       <c r="R23" t="n">
-        <v>6359096</v>
+        <v>6359087</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3243,10 +3234,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308186</v>
+        <v>120308180</v>
       </c>
       <c r="B24" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3255,41 +3246,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702315</v>
+        <v>702288</v>
       </c>
       <c r="R24" t="n">
-        <v>6359085</v>
+        <v>6359071</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308216</v>
+        <v>120308211</v>
       </c>
       <c r="B25" t="n">
         <v>108811</v>
@@ -3383,17 +3383,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702411</v>
+        <v>702376</v>
       </c>
       <c r="R25" t="n">
-        <v>6359095</v>
+        <v>6359086</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3457,7 +3466,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308202</v>
+        <v>120308206</v>
       </c>
       <c r="B26" t="n">
         <v>97905</v>
@@ -3492,7 +3501,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3506,10 +3515,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702373</v>
+        <v>702378</v>
       </c>
       <c r="R26" t="n">
-        <v>6359092</v>
+        <v>6359096</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3573,7 +3582,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308184</v>
+        <v>120308207</v>
       </c>
       <c r="B27" t="n">
         <v>108811</v>
@@ -3606,20 +3615,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702300</v>
+        <v>702378</v>
       </c>
       <c r="R27" t="n">
-        <v>6359068</v>
+        <v>6359096</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3680,10 +3698,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308199</v>
+        <v>120308184</v>
       </c>
       <c r="B28" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,47 +3710,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702363</v>
+        <v>702300</v>
       </c>
       <c r="R28" t="n">
-        <v>6359087</v>
+        <v>6359068</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3796,7 +3805,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308211</v>
+        <v>120308189</v>
       </c>
       <c r="B29" t="n">
         <v>108811</v>
@@ -3829,26 +3838,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702376</v>
+        <v>702314</v>
       </c>
       <c r="R29" t="n">
-        <v>6359086</v>
+        <v>6359093</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308189</v>
+        <v>120308200</v>
       </c>
       <c r="B30" t="n">
         <v>108811</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702314</v>
+        <v>702373</v>
       </c>
       <c r="R30" t="n">
-        <v>6359093</v>
+        <v>6359092</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120419627</v>
+        <v>120419636</v>
       </c>
       <c r="B31" t="n">
-        <v>90600</v>
+        <v>86367</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702369</v>
+        <v>702224</v>
       </c>
       <c r="R31" t="n">
-        <v>6359158</v>
+        <v>6358856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120419629</v>
+        <v>120419631</v>
       </c>
       <c r="B32" t="n">
-        <v>87408</v>
+        <v>90033</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4137,25 +4137,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>239233</v>
+        <v>2009</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702269</v>
+        <v>702248</v>
       </c>
       <c r="R32" t="n">
-        <v>6359044</v>
+        <v>6359026</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120419638</v>
+        <v>120419634</v>
       </c>
       <c r="B33" t="n">
-        <v>86282</v>
+        <v>86396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4243,25 +4243,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3712</v>
+        <v>473</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702258</v>
+        <v>702277</v>
       </c>
       <c r="R33" t="n">
-        <v>6358853</v>
+        <v>6358938</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120419636</v>
+        <v>120419628</v>
       </c>
       <c r="B34" t="n">
-        <v>86367</v>
+        <v>86449</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,25 +4349,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702224</v>
+        <v>702321</v>
       </c>
       <c r="R34" t="n">
-        <v>6358856</v>
+        <v>6359134</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120419628</v>
+        <v>120419627</v>
       </c>
       <c r="B35" t="n">
-        <v>86449</v>
+        <v>90600</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4459,21 +4459,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702321</v>
+        <v>702369</v>
       </c>
       <c r="R35" t="n">
-        <v>6359134</v>
+        <v>6359158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120419637</v>
+        <v>120419635</v>
       </c>
       <c r="B36" t="n">
-        <v>86373</v>
+        <v>86486</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,21 +4565,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702224</v>
+        <v>702277</v>
       </c>
       <c r="R36" t="n">
-        <v>6358856</v>
+        <v>6358938</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120419635</v>
+        <v>120419638</v>
       </c>
       <c r="B37" t="n">
-        <v>86486</v>
+        <v>86282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4667,25 +4667,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702277</v>
+        <v>702258</v>
       </c>
       <c r="R37" t="n">
-        <v>6358938</v>
+        <v>6358853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120419634</v>
+        <v>120419629</v>
       </c>
       <c r="B38" t="n">
-        <v>86396</v>
+        <v>87408</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>473</v>
+        <v>239233</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Ekvaxskivling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Hygrophorus cossus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Sowerby) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702277</v>
+        <v>702269</v>
       </c>
       <c r="R38" t="n">
-        <v>6358938</v>
+        <v>6359044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120419631</v>
+        <v>120419637</v>
       </c>
       <c r="B39" t="n">
-        <v>90033</v>
+        <v>86373</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2009</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702248</v>
+        <v>702224</v>
       </c>
       <c r="R39" t="n">
-        <v>6359026</v>
+        <v>6358856</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308195</v>
+        <v>120308180</v>
       </c>
       <c r="B15" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,41 +2247,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702354</v>
+        <v>702288</v>
       </c>
       <c r="R15" t="n">
-        <v>6359099</v>
+        <v>6359071</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2342,10 +2351,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308199</v>
+        <v>120308207</v>
       </c>
       <c r="B16" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,30 +2363,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2391,13 +2400,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702363</v>
+        <v>702378</v>
       </c>
       <c r="R16" t="n">
-        <v>6359087</v>
+        <v>6359096</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2458,10 +2467,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308178</v>
+        <v>120308189</v>
       </c>
       <c r="B17" t="n">
-        <v>97908</v>
+        <v>108811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,47 +2479,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702283</v>
+        <v>702314</v>
       </c>
       <c r="R17" t="n">
-        <v>6359063</v>
+        <v>6359093</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308166</v>
+        <v>120308200</v>
       </c>
       <c r="B18" t="n">
         <v>108811</v>
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702247</v>
+        <v>702373</v>
       </c>
       <c r="R18" t="n">
-        <v>6359023</v>
+        <v>6359092</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308216</v>
+        <v>120308206</v>
       </c>
       <c r="B19" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2693,38 +2693,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702411</v>
+        <v>702378</v>
       </c>
       <c r="R19" t="n">
-        <v>6359095</v>
+        <v>6359096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2788,10 +2797,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308202</v>
+        <v>120308184</v>
       </c>
       <c r="B20" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,50 +2809,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702373</v>
+        <v>702300</v>
       </c>
       <c r="R20" t="n">
-        <v>6359092</v>
+        <v>6359068</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308186</v>
+        <v>120308178</v>
       </c>
       <c r="B21" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,38 +2916,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702315</v>
+        <v>702283</v>
       </c>
       <c r="R21" t="n">
-        <v>6359085</v>
+        <v>6359063</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3127,7 +3136,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308197</v>
+        <v>120308195</v>
       </c>
       <c r="B23" t="n">
         <v>108811</v>
@@ -3167,13 +3176,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702363</v>
+        <v>702354</v>
       </c>
       <c r="R23" t="n">
-        <v>6359087</v>
+        <v>6359099</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3234,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308180</v>
+        <v>120308166</v>
       </c>
       <c r="B24" t="n">
-        <v>97908</v>
+        <v>108811</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3246,50 +3255,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702288</v>
+        <v>702247</v>
       </c>
       <c r="R24" t="n">
-        <v>6359071</v>
+        <v>6359023</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308206</v>
+        <v>120308197</v>
       </c>
       <c r="B26" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,50 +3478,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702378</v>
+        <v>702363</v>
       </c>
       <c r="R26" t="n">
-        <v>6359096</v>
+        <v>6359087</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3582,7 +3573,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308207</v>
+        <v>120308186</v>
       </c>
       <c r="B27" t="n">
         <v>108811</v>
@@ -3615,26 +3606,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702378</v>
+        <v>702315</v>
       </c>
       <c r="R27" t="n">
-        <v>6359096</v>
+        <v>6359085</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3698,7 +3680,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308184</v>
+        <v>120308216</v>
       </c>
       <c r="B28" t="n">
         <v>108811</v>
@@ -3738,13 +3720,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702300</v>
+        <v>702411</v>
       </c>
       <c r="R28" t="n">
-        <v>6359068</v>
+        <v>6359095</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3805,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308189</v>
+        <v>120308199</v>
       </c>
       <c r="B29" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,41 +3799,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702314</v>
+        <v>702363</v>
       </c>
       <c r="R29" t="n">
-        <v>6359093</v>
+        <v>6359087</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3912,10 +3903,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308200</v>
+        <v>120308202</v>
       </c>
       <c r="B30" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3924,28 +3915,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120419636</v>
+        <v>120419631</v>
       </c>
       <c r="B31" t="n">
-        <v>86367</v>
+        <v>90033</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>449</v>
+        <v>2009</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702224</v>
+        <v>702248</v>
       </c>
       <c r="R31" t="n">
-        <v>6358856</v>
+        <v>6359026</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120419631</v>
+        <v>120419637</v>
       </c>
       <c r="B32" t="n">
-        <v>90033</v>
+        <v>86373</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4137,25 +4137,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2009</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702248</v>
+        <v>702224</v>
       </c>
       <c r="R32" t="n">
-        <v>6359026</v>
+        <v>6358856</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120419628</v>
+        <v>120419629</v>
       </c>
       <c r="B34" t="n">
-        <v>86449</v>
+        <v>87408</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,21 +4353,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>239233</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ekvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hygrophorus cossus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Sowerby) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702321</v>
+        <v>702269</v>
       </c>
       <c r="R34" t="n">
-        <v>6359134</v>
+        <v>6359044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120419627</v>
+        <v>120419638</v>
       </c>
       <c r="B35" t="n">
-        <v>90600</v>
+        <v>86282</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4455,25 +4455,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>3712</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702369</v>
+        <v>702258</v>
       </c>
       <c r="R35" t="n">
-        <v>6359158</v>
+        <v>6358853</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120419635</v>
+        <v>120419627</v>
       </c>
       <c r="B36" t="n">
-        <v>86486</v>
+        <v>90600</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4561,25 +4561,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3767</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702277</v>
+        <v>702369</v>
       </c>
       <c r="R36" t="n">
-        <v>6358938</v>
+        <v>6359158</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120419638</v>
+        <v>120419636</v>
       </c>
       <c r="B37" t="n">
-        <v>86282</v>
+        <v>86367</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4667,25 +4667,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702258</v>
+        <v>702224</v>
       </c>
       <c r="R37" t="n">
-        <v>6358853</v>
+        <v>6358856</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120419629</v>
+        <v>120419628</v>
       </c>
       <c r="B38" t="n">
-        <v>87408</v>
+        <v>86449</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>239233</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702269</v>
+        <v>702321</v>
       </c>
       <c r="R38" t="n">
-        <v>6359044</v>
+        <v>6359134</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120419637</v>
+        <v>120419635</v>
       </c>
       <c r="B39" t="n">
-        <v>86373</v>
+        <v>86486</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4883,21 +4883,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702224</v>
+        <v>702277</v>
       </c>
       <c r="R39" t="n">
-        <v>6358856</v>
+        <v>6358938</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308180</v>
+        <v>120308206</v>
       </c>
       <c r="B15" t="n">
-        <v>97908</v>
+        <v>97905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702288</v>
+        <v>702378</v>
       </c>
       <c r="R15" t="n">
-        <v>6359071</v>
+        <v>6359096</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308207</v>
+        <v>120308197</v>
       </c>
       <c r="B16" t="n">
         <v>108811</v>
@@ -2384,29 +2384,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702378</v>
+        <v>702363</v>
       </c>
       <c r="R16" t="n">
-        <v>6359096</v>
+        <v>6359087</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2467,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308189</v>
+        <v>120308191</v>
       </c>
       <c r="B17" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2479,28 +2470,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308200</v>
+        <v>120308178</v>
       </c>
       <c r="B18" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,38 +2586,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702373</v>
+        <v>702283</v>
       </c>
       <c r="R18" t="n">
-        <v>6359092</v>
+        <v>6359063</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2681,10 +2690,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308206</v>
+        <v>120308200</v>
       </c>
       <c r="B19" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2693,47 +2702,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702378</v>
+        <v>702373</v>
       </c>
       <c r="R19" t="n">
-        <v>6359096</v>
+        <v>6359092</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308184</v>
+        <v>120308180</v>
       </c>
       <c r="B20" t="n">
-        <v>108811</v>
+        <v>97908</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,41 +2809,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702300</v>
+        <v>702288</v>
       </c>
       <c r="R20" t="n">
-        <v>6359068</v>
+        <v>6359071</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2904,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308178</v>
+        <v>120308199</v>
       </c>
       <c r="B21" t="n">
-        <v>97908</v>
+        <v>97905</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2920,21 +2929,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2953,13 +2962,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702283</v>
+        <v>702363</v>
       </c>
       <c r="R21" t="n">
-        <v>6359063</v>
+        <v>6359087</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3020,10 +3029,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308191</v>
+        <v>120308184</v>
       </c>
       <c r="B22" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,50 +3041,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702314</v>
+        <v>702300</v>
       </c>
       <c r="R22" t="n">
-        <v>6359093</v>
+        <v>6359068</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308195</v>
+        <v>120308211</v>
       </c>
       <c r="B23" t="n">
         <v>108811</v>
@@ -3169,17 +3169,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702354</v>
+        <v>702376</v>
       </c>
       <c r="R23" t="n">
-        <v>6359099</v>
+        <v>6359086</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3243,7 +3252,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308166</v>
+        <v>120308186</v>
       </c>
       <c r="B24" t="n">
         <v>108811</v>
@@ -3283,13 +3292,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702247</v>
+        <v>702315</v>
       </c>
       <c r="R24" t="n">
-        <v>6359023</v>
+        <v>6359085</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3350,7 +3359,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308211</v>
+        <v>120308207</v>
       </c>
       <c r="B25" t="n">
         <v>108811</v>
@@ -3385,7 +3394,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3399,10 +3408,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702376</v>
+        <v>702378</v>
       </c>
       <c r="R25" t="n">
-        <v>6359086</v>
+        <v>6359096</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3466,7 +3475,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308197</v>
+        <v>120308216</v>
       </c>
       <c r="B26" t="n">
         <v>108811</v>
@@ -3506,13 +3515,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702363</v>
+        <v>702411</v>
       </c>
       <c r="R26" t="n">
-        <v>6359087</v>
+        <v>6359095</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3573,7 +3582,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308186</v>
+        <v>120308166</v>
       </c>
       <c r="B27" t="n">
         <v>108811</v>
@@ -3613,13 +3622,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702315</v>
+        <v>702247</v>
       </c>
       <c r="R27" t="n">
-        <v>6359085</v>
+        <v>6359023</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3680,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308216</v>
+        <v>120308202</v>
       </c>
       <c r="B28" t="n">
-        <v>108811</v>
+        <v>97905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,38 +3701,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702411</v>
+        <v>702373</v>
       </c>
       <c r="R28" t="n">
-        <v>6359095</v>
+        <v>6359092</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3787,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308199</v>
+        <v>120308195</v>
       </c>
       <c r="B29" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3799,50 +3817,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702363</v>
+        <v>702354</v>
       </c>
       <c r="R29" t="n">
-        <v>6359087</v>
+        <v>6359099</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3903,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308202</v>
+        <v>120308189</v>
       </c>
       <c r="B30" t="n">
-        <v>97905</v>
+        <v>108811</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3915,47 +3924,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702373</v>
+        <v>702314</v>
       </c>
       <c r="R30" t="n">
-        <v>6359092</v>
+        <v>6359093</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120419631</v>
+        <v>120419634</v>
       </c>
       <c r="B31" t="n">
-        <v>90033</v>
+        <v>86396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2009</v>
+        <v>473</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702248</v>
+        <v>702277</v>
       </c>
       <c r="R31" t="n">
-        <v>6359026</v>
+        <v>6358938</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120419634</v>
+        <v>120419629</v>
       </c>
       <c r="B33" t="n">
-        <v>86396</v>
+        <v>87408</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,21 +4247,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>473</v>
+        <v>239233</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Ekvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Hygrophorus cossus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Sowerby) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702277</v>
+        <v>702269</v>
       </c>
       <c r="R33" t="n">
-        <v>6358938</v>
+        <v>6359044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120419629</v>
+        <v>120419635</v>
       </c>
       <c r="B34" t="n">
-        <v>87408</v>
+        <v>86486</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,25 +4349,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>239233</v>
+        <v>3767</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702269</v>
+        <v>702277</v>
       </c>
       <c r="R34" t="n">
-        <v>6359044</v>
+        <v>6358938</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120419638</v>
+        <v>120419636</v>
       </c>
       <c r="B35" t="n">
-        <v>86282</v>
+        <v>86367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4455,25 +4455,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702258</v>
+        <v>702224</v>
       </c>
       <c r="R35" t="n">
-        <v>6358853</v>
+        <v>6358856</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120419627</v>
+        <v>120419638</v>
       </c>
       <c r="B36" t="n">
-        <v>90600</v>
+        <v>86282</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4561,25 +4561,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>3712</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702369</v>
+        <v>702258</v>
       </c>
       <c r="R36" t="n">
-        <v>6359158</v>
+        <v>6358853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120419636</v>
+        <v>120419628</v>
       </c>
       <c r="B37" t="n">
-        <v>86367</v>
+        <v>86449</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4667,25 +4667,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702224</v>
+        <v>702321</v>
       </c>
       <c r="R37" t="n">
-        <v>6358856</v>
+        <v>6359134</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120419628</v>
+        <v>120419627</v>
       </c>
       <c r="B38" t="n">
-        <v>86449</v>
+        <v>90600</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702321</v>
+        <v>702369</v>
       </c>
       <c r="R38" t="n">
-        <v>6359134</v>
+        <v>6359158</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120419635</v>
+        <v>120419631</v>
       </c>
       <c r="B39" t="n">
-        <v>86486</v>
+        <v>90033</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3767</v>
+        <v>2009</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702277</v>
+        <v>702248</v>
       </c>
       <c r="R39" t="n">
-        <v>6358938</v>
+        <v>6359026</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14846064</v>
+        <v>120644809</v>
       </c>
       <c r="B2" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2:a Mskylt till 3:e M, Sojskvear, Gtl</t>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702284.9844306849</v>
+        <v>702278</v>
       </c>
       <c r="R2" t="n">
-        <v>6358838.392368108</v>
+        <v>6358911</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sträcka ca 230m</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,71 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14846063</v>
+        <v>120644847</v>
       </c>
       <c r="B3" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102018</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2:a Mskylt till 3:e M, Sojskvear, Gtl</t>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702284.9844306849</v>
+        <v>702207</v>
       </c>
       <c r="R3" t="n">
-        <v>6358838.392368108</v>
+        <v>6358908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sträcka ca 230m</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1339313</v>
+        <v>120644959</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lojsta, öster graunvik, Gtl</t>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702245.0202283971</v>
+        <v>702245</v>
       </c>
       <c r="R4" t="n">
-        <v>6358846.692040291</v>
+        <v>6358873</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,74 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åke Edvinsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16869292</v>
+        <v>120419636</v>
       </c>
       <c r="B5" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
+          <t>Granuvik, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702321.8020304462</v>
+        <v>702224</v>
       </c>
       <c r="R5" t="n">
-        <v>6358893.748632038</v>
+        <v>6358856</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,62 +1051,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97389934</v>
+        <v>120419634</v>
       </c>
       <c r="B6" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>473</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvie Källmyr V, Gtl</t>
+          <t>Granuvik, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702288.5826899479</v>
+        <v>702277</v>
       </c>
       <c r="R6" t="n">
-        <v>6359127.333897938</v>
+        <v>6358938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,54 +1160,53 @@
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97389933</v>
+        <v>120644922</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>473</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvie Källmyr V, Gtl</t>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702274.5569136152</v>
+        <v>702234</v>
       </c>
       <c r="R7" t="n">
-        <v>6359126.099881634</v>
+        <v>6358865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,22 +1233,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,27 +1253,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104340635</v>
+        <v>120419631</v>
       </c>
       <c r="B8" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,38 +1276,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>2009</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta Kvie 218, Gotland, Gtl</t>
+          <t>Granuvik, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702298.5601278237</v>
+        <v>702248</v>
       </c>
       <c r="R8" t="n">
-        <v>6358892.599739577</v>
+        <v>6359026</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,19 +1333,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,27 +1350,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Brian Johnson, Gillis Aronsson, Helena Björnström, Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104340681</v>
+        <v>120644805</v>
       </c>
       <c r="B9" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,38 +1377,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>2009</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta Kvie 218, Gotland, Gtl</t>
+          <t>Graunvik, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702333.0745425595</v>
+        <v>702358</v>
       </c>
       <c r="R9" t="n">
-        <v>6358939.730185653</v>
+        <v>6359059</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,22 +1431,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,27 +1461,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Brian Johnson, Gillis Aronsson, Helena Björnström, Michael Krikorev</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104469398</v>
+        <v>97389934</v>
       </c>
       <c r="B10" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,37 +1484,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Kvie Källmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702294.8298899691</v>
+        <v>702289</v>
       </c>
       <c r="R10" t="n">
-        <v>6358891.333823047</v>
+        <v>6359127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,22 +1538,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,84 +1552,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104469395</v>
+        <v>104340635</v>
       </c>
       <c r="B11" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Lojsta Kvie 218, Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702338.6200288848</v>
+        <v>702299</v>
       </c>
       <c r="R11" t="n">
-        <v>6358948.115776507</v>
+        <v>6358893</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,105 +1639,78 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Brian Johnson, Gillis Aronsson, Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104469397</v>
+        <v>104340681</v>
       </c>
       <c r="B12" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248955</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Lojsta Kvie 218, Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702326.0870565551</v>
+        <v>702333</v>
       </c>
       <c r="R12" t="n">
-        <v>6358916.672665195</v>
+        <v>6358940</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,105 +1737,77 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Brian Johnson, Gillis Aronsson, Helena Björnström, Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104469396</v>
+        <v>16869289</v>
       </c>
       <c r="B13" t="n">
-        <v>88943</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5747</v>
+        <v>3712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702326.0870565551</v>
+        <v>702340</v>
       </c>
       <c r="R13" t="n">
-        <v>6358916.672665195</v>
+        <v>6358873</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2053,27 +1826,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Hemse</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,43 +1845,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104469399</v>
+        <v>120419638</v>
       </c>
       <c r="B14" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,37 +1874,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Granuvik, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702282.478156589</v>
+        <v>702258</v>
       </c>
       <c r="R14" t="n">
-        <v>6358889.101014115</v>
+        <v>6358853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,45 +1931,29 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2235,62 +1964,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120308202</v>
+        <v>120644923</v>
       </c>
       <c r="B15" t="n">
-        <v>97980</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219797</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702373</v>
+        <v>702223</v>
       </c>
       <c r="R15" t="n">
-        <v>6359092</v>
+        <v>6358866</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2314,12 +2029,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,83 +2045,73 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120308211</v>
+        <v>16869292</v>
       </c>
       <c r="B16" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702376</v>
+        <v>702322</v>
       </c>
       <c r="R16" t="n">
-        <v>6359086</v>
+        <v>6358894</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2430,12 +2135,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,74 +2151,64 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120308186</v>
+        <v>120645098</v>
       </c>
       <c r="B17" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Graunvik, Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702315</v>
+        <v>702283</v>
       </c>
       <c r="R17" t="n">
-        <v>6359085</v>
+        <v>6358896</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2537,12 +2232,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,83 +2248,64 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120308206</v>
+        <v>120419635</v>
       </c>
       <c r="B18" t="n">
-        <v>97980</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219797</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Granuvik, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702378</v>
+        <v>702277</v>
       </c>
       <c r="R18" t="n">
-        <v>6359096</v>
+        <v>6358938</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2653,12 +2329,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,36 +2345,30 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120308191</v>
+        <v>16869291</v>
       </c>
       <c r="B19" t="n">
-        <v>97980</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,21 +2376,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219797</v>
+        <v>4188</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2730,22 +2400,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702314</v>
+        <v>702357</v>
       </c>
       <c r="R19" t="n">
-        <v>6359093</v>
+        <v>6358890</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2764,17 +2434,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Hemse</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,74 +2455,64 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120308200</v>
+        <v>1339313</v>
       </c>
       <c r="B20" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Lojsta, öster graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702373</v>
+        <v>702245</v>
       </c>
       <c r="R20" t="n">
-        <v>6359092</v>
+        <v>6358847</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2876,12 +2536,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,71 +2552,64 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120308184</v>
+        <v>104469398</v>
       </c>
       <c r="B21" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702300</v>
+        <v>702295</v>
       </c>
       <c r="R21" t="n">
-        <v>6359068</v>
+        <v>6358892</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2983,12 +2636,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2997,38 +2650,38 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120308216</v>
+        <v>120419627</v>
       </c>
       <c r="B22" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,37 +2689,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Granuvik, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>702411</v>
+        <v>702369</v>
       </c>
       <c r="R22" t="n">
-        <v>6359095</v>
+        <v>6359158</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,12 +2743,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,83 +2759,71 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120308207</v>
+        <v>104469396</v>
       </c>
       <c r="B23" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>702378</v>
+        <v>702326</v>
       </c>
       <c r="R23" t="n">
-        <v>6359096</v>
+        <v>6358917</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3206,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3220,73 +2861,78 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120308166</v>
+        <v>120308386</v>
       </c>
       <c r="B24" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>702247</v>
+        <v>702424</v>
       </c>
       <c r="R24" t="n">
-        <v>6359023</v>
+        <v>6359103</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,7 +2954,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Hemse</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3321,6 +2967,11 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Högstubbe med spillkråkehål och insektsgnag.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3329,11 +2980,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3350,15 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120308197</v>
+        <v>14846064</v>
       </c>
       <c r="B25" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3366,34 +3007,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>2:a Mskylt till 3:e M, Sojskvear, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>702363</v>
+        <v>702285</v>
       </c>
       <c r="R25" t="n">
-        <v>6359087</v>
+        <v>6358838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3420,12 +3070,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2011-07-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2011-07-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Sträcka ca 230m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,74 +3091,73 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120308189</v>
+        <v>14846063</v>
       </c>
       <c r="B26" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>102018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>2:a Mskylt till 3:e M, Sojskvear, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702314</v>
+        <v>702285</v>
       </c>
       <c r="R26" t="n">
-        <v>6359093</v>
+        <v>6358838</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3527,12 +3181,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2011-07-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2011-07-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sträcka ca 230m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3543,71 +3202,70 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ingrid Angelöf</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308195</v>
+        <v>120308191</v>
       </c>
       <c r="B27" t="n">
-        <v>108886</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>219797</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702354</v>
+        <v>702314</v>
       </c>
       <c r="R27" t="n">
-        <v>6359099</v>
+        <v>6359093</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3671,15 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308180</v>
+        <v>120308199</v>
       </c>
       <c r="B28" t="n">
-        <v>97983</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,26 +3340,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3720,13 +3373,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702288</v>
+        <v>702363</v>
       </c>
       <c r="R28" t="n">
-        <v>6359071</v>
+        <v>6359087</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3787,15 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308199</v>
+        <v>120308202</v>
       </c>
       <c r="B29" t="n">
-        <v>97980</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3822,7 +3470,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3836,13 +3484,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702363</v>
+        <v>702373</v>
       </c>
       <c r="R29" t="n">
-        <v>6359087</v>
+        <v>6359092</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3903,15 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308178</v>
+        <v>120308206</v>
       </c>
       <c r="B30" t="n">
-        <v>97983</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,26 +3562,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3952,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702283</v>
+        <v>702378</v>
       </c>
       <c r="R30" t="n">
-        <v>6359063</v>
+        <v>6359096</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4019,50 +3662,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120419629</v>
+        <v>97389933</v>
       </c>
       <c r="B31" t="n">
-        <v>88484</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>239233</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Kvie Källmyr V, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702269</v>
+        <v>702275</v>
       </c>
       <c r="R31" t="n">
-        <v>6359044</v>
+        <v>6359126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +3727,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4117,23 +3755,14 @@
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120419631</v>
+        <v>120308178</v>
       </c>
       <c r="B32" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,37 +3770,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2009</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702248</v>
+        <v>702283</v>
       </c>
       <c r="R32" t="n">
-        <v>6359026</v>
+        <v>6359063</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4195,12 +3833,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,73 +3849,78 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120419627</v>
+        <v>120308180</v>
       </c>
       <c r="B33" t="n">
-        <v>90664</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702369</v>
+        <v>702288</v>
       </c>
       <c r="R33" t="n">
-        <v>6359158</v>
+        <v>6359071</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4301,12 +3944,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4317,35 +3960,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120419628</v>
+        <v>120308166</v>
       </c>
       <c r="B34" t="n">
-        <v>86227</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,34 +3992,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702321</v>
+        <v>702247</v>
       </c>
       <c r="R34" t="n">
-        <v>6359134</v>
+        <v>6359023</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4407,12 +4046,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4423,70 +4062,66 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120419637</v>
+        <v>120308184</v>
       </c>
       <c r="B35" t="n">
-        <v>86150</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>248956</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702224</v>
+        <v>702300</v>
       </c>
       <c r="R35" t="n">
-        <v>6358856</v>
+        <v>6359068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4513,12 +4148,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4529,73 +4164,69 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120419636</v>
+        <v>120308186</v>
       </c>
       <c r="B36" t="n">
-        <v>86144</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702224</v>
+        <v>702315</v>
       </c>
       <c r="R36" t="n">
-        <v>6358856</v>
+        <v>6359085</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4619,12 +4250,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,73 +4266,69 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120419638</v>
+        <v>120308189</v>
       </c>
       <c r="B37" t="n">
-        <v>86056</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3712</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702258</v>
+        <v>702314</v>
       </c>
       <c r="R37" t="n">
-        <v>6358853</v>
+        <v>6359093</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4725,12 +4352,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4741,73 +4368,69 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120419635</v>
+        <v>120308195</v>
       </c>
       <c r="B38" t="n">
-        <v>86264</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3767</v>
+        <v>220299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702277</v>
+        <v>702354</v>
       </c>
       <c r="R38" t="n">
-        <v>6358938</v>
+        <v>6359099</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4831,12 +4454,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4847,35 +4470,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120419634</v>
+        <v>120308197</v>
       </c>
       <c r="B39" t="n">
-        <v>86173</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,34 +4502,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>473</v>
+        <v>220299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702277</v>
+        <v>702363</v>
       </c>
       <c r="R39" t="n">
-        <v>6358938</v>
+        <v>6359087</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4937,12 +4556,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,73 +4572,69 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120644847</v>
+        <v>120308200</v>
       </c>
       <c r="B40" t="n">
-        <v>86106</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>424</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>702207</v>
+        <v>702373</v>
       </c>
       <c r="R40" t="n">
-        <v>6358908</v>
+        <v>6359092</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5043,12 +4658,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5059,69 +4674,78 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120644923</v>
+        <v>120308207</v>
       </c>
       <c r="B41" t="n">
-        <v>86084</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3712</v>
+        <v>220299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>702223</v>
+        <v>702378</v>
       </c>
       <c r="R41" t="n">
-        <v>6358866</v>
+        <v>6359096</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5145,12 +4769,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5161,69 +4785,78 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120645058</v>
+        <v>120308211</v>
       </c>
       <c r="B42" t="n">
-        <v>86174</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248956</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>702279</v>
+        <v>702376</v>
       </c>
       <c r="R42" t="n">
-        <v>6358899</v>
+        <v>6359086</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5247,47 +4880,47 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120644922</v>
+        <v>120308216</v>
       </c>
       <c r="B43" t="n">
-        <v>86197</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5295,37 +4928,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>473</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>702234</v>
+        <v>702411</v>
       </c>
       <c r="R43" t="n">
-        <v>6358865</v>
+        <v>6359095</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5349,12 +4982,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5365,69 +4998,78 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120644805</v>
+        <v>120308220</v>
       </c>
       <c r="B44" t="n">
-        <v>90118</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2009</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Graunvik, Graunvik, Gtl</t>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>702358</v>
+        <v>702423</v>
       </c>
       <c r="R44" t="n">
-        <v>6359059</v>
+        <v>6359097</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5446,27 +5088,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Hemse</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5477,69 +5109,78 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120644809</v>
+        <v>120308223</v>
       </c>
       <c r="B45" t="n">
-        <v>86106</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>424</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>702278</v>
+        <v>702425</v>
       </c>
       <c r="R45" t="n">
-        <v>6358911</v>
+        <v>6359055</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5558,17 +5199,17 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Hemse</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,69 +5220,78 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120644959</v>
+        <v>120308226</v>
       </c>
       <c r="B46" t="n">
-        <v>86106</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>702245</v>
+        <v>702431</v>
       </c>
       <c r="R46" t="n">
-        <v>6358873</v>
+        <v>6359070</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5660,17 +5310,17 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Hemse</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5681,66 +5331,69 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120645098</v>
+        <v>104469397</v>
       </c>
       <c r="B47" t="n">
-        <v>86024</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3762</v>
+        <v>248955</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Graunvik, Graunvik, Gtl</t>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>702283</v>
+        <v>702326</v>
       </c>
       <c r="R47" t="n">
-        <v>6358896</v>
+        <v>6358917</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5767,12 +5420,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5781,21 +5434,763 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120419637</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>702224</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6358856</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120645042</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Graunvik, Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>702169</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6358801</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120645058</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>702279</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6358899</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>16869288</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>702340</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6358873</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>104469395</v>
+      </c>
+      <c r="B52" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>702339</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6358948</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>104469399</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>702283</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6358889</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120419628</v>
+      </c>
+      <c r="B54" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>702321</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6359134</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3107,57 +3107,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>14846063</v>
+        <v>134682296</v>
       </c>
       <c r="B26" t="n">
-        <v>45044</v>
+        <v>43472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102018</v>
+        <v>101242</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2:a Mskylt till 3:e M, Sojskvear, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>702285</v>
+        <v>702215</v>
       </c>
       <c r="R26" t="n">
-        <v>6358838</v>
+        <v>6358846</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3181,17 +3172,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Sträcka ca 230m</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3206,66 +3207,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ingrid Angelöf</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120308191</v>
+        <v>134682301</v>
       </c>
       <c r="B27" t="n">
-        <v>99093</v>
+        <v>43472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219797</v>
+        <v>101242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>702314</v>
+        <v>702195</v>
       </c>
       <c r="R27" t="n">
-        <v>6359093</v>
+        <v>6358845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3292,12 +3284,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3308,78 +3315,64 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120308199</v>
+        <v>134682306</v>
       </c>
       <c r="B28" t="n">
-        <v>99093</v>
+        <v>43472</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219797</v>
+        <v>101242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>702363</v>
+        <v>702180</v>
       </c>
       <c r="R28" t="n">
-        <v>6359087</v>
+        <v>6358863</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3403,12 +3396,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3419,75 +3422,61 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120308202</v>
+        <v>134682309</v>
       </c>
       <c r="B29" t="n">
-        <v>99093</v>
+        <v>43472</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219797</v>
+        <v>101242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>702373</v>
+        <v>702162</v>
       </c>
       <c r="R29" t="n">
-        <v>6359092</v>
+        <v>6358870</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3514,12 +3503,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3530,75 +3529,61 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120308206</v>
+        <v>134682312</v>
       </c>
       <c r="B30" t="n">
-        <v>99093</v>
+        <v>43472</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>101242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>702378</v>
+        <v>702152</v>
       </c>
       <c r="R30" t="n">
-        <v>6359096</v>
+        <v>6358853</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,12 +3610,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,69 +3641,64 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97389933</v>
+        <v>134682316</v>
       </c>
       <c r="B31" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvie Källmyr V, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>702275</v>
+        <v>702158</v>
       </c>
       <c r="R31" t="n">
-        <v>6359126</v>
+        <v>6358845</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3727,12 +3722,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3747,66 +3757,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120308178</v>
+        <v>134682318</v>
       </c>
       <c r="B32" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>702283</v>
+        <v>702163</v>
       </c>
       <c r="R32" t="n">
-        <v>6359063</v>
+        <v>6358840</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3833,12 +3834,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3849,78 +3865,64 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308180</v>
+        <v>134682325</v>
       </c>
       <c r="B33" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>702288</v>
+        <v>702177</v>
       </c>
       <c r="R33" t="n">
-        <v>6359071</v>
+        <v>6358825</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3944,12 +3946,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3960,31 +3972,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308166</v>
+        <v>134682328</v>
       </c>
       <c r="B34" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3992,37 +3999,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>702247</v>
+        <v>702189</v>
       </c>
       <c r="R34" t="n">
-        <v>6359023</v>
+        <v>6358854</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4046,12 +4053,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,31 +4079,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120308184</v>
+        <v>134682330</v>
       </c>
       <c r="B35" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4094,37 +4106,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>702300</v>
+        <v>702188</v>
       </c>
       <c r="R35" t="n">
-        <v>6359068</v>
+        <v>6358871</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4148,12 +4160,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4164,31 +4191,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120308186</v>
+        <v>134682335</v>
       </c>
       <c r="B36" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,34 +4218,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>702315</v>
+        <v>702161</v>
       </c>
       <c r="R36" t="n">
-        <v>6359085</v>
+        <v>6358893</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4250,12 +4272,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4266,31 +4298,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120308189</v>
+        <v>134682340</v>
       </c>
       <c r="B37" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,34 +4325,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>702314</v>
+        <v>702208</v>
       </c>
       <c r="R37" t="n">
-        <v>6359093</v>
+        <v>6358902</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4352,12 +4379,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4368,31 +4405,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120308195</v>
+        <v>134682342</v>
       </c>
       <c r="B38" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4400,34 +4432,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>702354</v>
+        <v>702217</v>
       </c>
       <c r="R38" t="n">
-        <v>6359099</v>
+        <v>6358905</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4454,12 +4486,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4470,31 +4512,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120308197</v>
+        <v>134682347</v>
       </c>
       <c r="B39" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4502,37 +4539,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>702363</v>
+        <v>702223</v>
       </c>
       <c r="R39" t="n">
-        <v>6359087</v>
+        <v>6358910</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4556,12 +4593,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4572,31 +4619,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120308200</v>
+        <v>134682349</v>
       </c>
       <c r="B40" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4604,34 +4646,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>702373</v>
+        <v>702256</v>
       </c>
       <c r="R40" t="n">
-        <v>6359092</v>
+        <v>6358934</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4658,12 +4700,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4674,31 +4726,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120308207</v>
+        <v>134682353</v>
       </c>
       <c r="B41" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4706,43 +4753,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>702378</v>
+        <v>702236</v>
       </c>
       <c r="R41" t="n">
-        <v>6359096</v>
+        <v>6359013</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4769,12 +4807,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4785,31 +4833,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120308211</v>
+        <v>134682355</v>
       </c>
       <c r="B42" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,43 +4860,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>702376</v>
+        <v>702236</v>
       </c>
       <c r="R42" t="n">
-        <v>6359086</v>
+        <v>6359020</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4880,12 +4914,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4896,31 +4940,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120308216</v>
+        <v>134682360</v>
       </c>
       <c r="B43" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4928,34 +4967,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>702411</v>
+        <v>702229</v>
       </c>
       <c r="R43" t="n">
-        <v>6359095</v>
+        <v>6359045</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4982,12 +5021,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4998,31 +5047,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120308220</v>
+        <v>134682362</v>
       </c>
       <c r="B44" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5030,43 +5074,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>702423</v>
+        <v>702213</v>
       </c>
       <c r="R44" t="n">
-        <v>6359097</v>
+        <v>6359052</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5088,17 +5123,27 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Hemse</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5109,31 +5154,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120308223</v>
+        <v>134682364</v>
       </c>
       <c r="B45" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,43 +5181,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>702425</v>
+        <v>702258</v>
       </c>
       <c r="R45" t="n">
-        <v>6359055</v>
+        <v>6359079</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5199,17 +5230,27 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Hemse</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5220,31 +5261,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120308226</v>
+        <v>134682370</v>
       </c>
       <c r="B46" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5252,43 +5288,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>702431</v>
+        <v>702281</v>
       </c>
       <c r="R46" t="n">
-        <v>6359070</v>
+        <v>6359062</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5310,17 +5337,27 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Hemse</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5331,72 +5368,64 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104469397</v>
+        <v>134682373</v>
       </c>
       <c r="B47" t="n">
-        <v>87291</v>
+        <v>43472</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248955</v>
+        <v>101242</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>702326</v>
+        <v>702273</v>
       </c>
       <c r="R47" t="n">
-        <v>6358917</v>
+        <v>6359050</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5420,12 +5449,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5434,76 +5473,66 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120419637</v>
+        <v>134682375</v>
       </c>
       <c r="B48" t="n">
-        <v>87262</v>
+        <v>43472</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>248956</v>
+        <v>101242</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>702224</v>
+        <v>702260</v>
       </c>
       <c r="R48" t="n">
-        <v>6358856</v>
+        <v>6359050</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5527,12 +5556,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5547,64 +5586,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120645042</v>
+        <v>134682379</v>
       </c>
       <c r="B49" t="n">
-        <v>87262</v>
+        <v>43472</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>248956</v>
+        <v>101242</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Graunvik, Graunvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>702169</v>
+        <v>702258</v>
       </c>
       <c r="R49" t="n">
-        <v>6358801</v>
+        <v>6359051</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5628,22 +5663,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5670,48 +5705,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120645058</v>
+        <v>134682380</v>
       </c>
       <c r="B50" t="n">
-        <v>87262</v>
+        <v>43472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>248956</v>
+        <v>101242</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>702279</v>
+        <v>702254</v>
       </c>
       <c r="R50" t="n">
-        <v>6358899</v>
+        <v>6359044</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5735,19 +5770,34 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -5755,22 +5805,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>16869288</v>
+        <v>134682384</v>
       </c>
       <c r="B51" t="n">
-        <v>87099</v>
+        <v>43472</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5778,46 +5828,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>249278</v>
+        <v>101242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>702340</v>
+        <v>702250</v>
       </c>
       <c r="R51" t="n">
-        <v>6358873</v>
+        <v>6359032</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5836,17 +5877,27 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Hemse</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5861,22 +5912,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104469395</v>
+        <v>134682386</v>
       </c>
       <c r="B52" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,40 +5935,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>702339</v>
+        <v>702240</v>
       </c>
       <c r="R52" t="n">
-        <v>6358948</v>
+        <v>6358943</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5941,12 +5989,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5955,38 +6018,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104469399</v>
+        <v>134682387</v>
       </c>
       <c r="B53" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5994,40 +6047,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>702283</v>
+        <v>702245</v>
       </c>
       <c r="R53" t="n">
-        <v>6358889</v>
+        <v>6358888</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,12 +6101,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6065,38 +6130,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120419628</v>
+        <v>134682389</v>
       </c>
       <c r="B54" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6104,37 +6159,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Granuvik, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>702321</v>
+        <v>702283</v>
       </c>
       <c r="R54" t="n">
-        <v>6359134</v>
+        <v>6358863</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6158,12 +6213,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6178,15 +6243,5482 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134682390</v>
+      </c>
+      <c r="B55" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>702291</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6358862</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134682391</v>
+      </c>
+      <c r="B56" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>702309</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6358868</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134682394</v>
+      </c>
+      <c r="B57" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>702340</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6358890</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134685337</v>
+      </c>
+      <c r="B58" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>702280</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6358858</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134685339</v>
+      </c>
+      <c r="B59" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>702326</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6358884</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134685341</v>
+      </c>
+      <c r="B60" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>702321</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6358922</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134685342</v>
+      </c>
+      <c r="B61" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>702334</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6358935</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134685343</v>
+      </c>
+      <c r="B62" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>702347</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6358924</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134685344</v>
+      </c>
+      <c r="B63" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>702348</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6358949</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134685345</v>
+      </c>
+      <c r="B64" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>702368</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6358970</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134685349</v>
+      </c>
+      <c r="B65" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>702406</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6359143</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134685351</v>
+      </c>
+      <c r="B66" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>702375</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6359200</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134685355</v>
+      </c>
+      <c r="B67" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>702245</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6359006</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134685356</v>
+      </c>
+      <c r="B68" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>702255</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6359034</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134685357</v>
+      </c>
+      <c r="B69" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>702268</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6359044</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134685358</v>
+      </c>
+      <c r="B70" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>702294</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6359063</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134685359</v>
+      </c>
+      <c r="B71" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>702254</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6359037</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134685360</v>
+      </c>
+      <c r="B72" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>702297</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6358889</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134685361</v>
+      </c>
+      <c r="B73" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>702315</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6358901</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134685362</v>
+      </c>
+      <c r="B74" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 922, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>702322</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6358910</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>14846063</v>
+      </c>
+      <c r="B75" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2:a Mskylt till 3:e M, Sojskvear, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>702285</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6358838</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2011-07-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2011-07-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Sträcka ca 230m</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ingrid Angelöf</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ingrid Angelöf</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120308191</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>702314</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6359093</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120308199</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>702363</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6359087</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120308202</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>702373</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6359092</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120308206</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>702378</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6359096</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>97389933</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kvie Källmyr V, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>702275</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6359126</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120308178</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>702283</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6359063</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120308180</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>702288</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6359071</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120308166</v>
+      </c>
+      <c r="B83" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>702247</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6359023</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120308184</v>
+      </c>
+      <c r="B84" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>702300</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6359068</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120308186</v>
+      </c>
+      <c r="B85" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>702315</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6359085</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120308189</v>
+      </c>
+      <c r="B86" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>702314</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6359093</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120308195</v>
+      </c>
+      <c r="B87" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>702354</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6359099</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120308197</v>
+      </c>
+      <c r="B88" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>702363</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6359087</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120308200</v>
+      </c>
+      <c r="B89" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>702373</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6359092</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120308207</v>
+      </c>
+      <c r="B90" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>702378</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6359096</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120308211</v>
+      </c>
+      <c r="B91" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>702376</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6359086</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120308216</v>
+      </c>
+      <c r="B92" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve 1:15 (2) (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>702411</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6359095</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120308220</v>
+      </c>
+      <c r="B93" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>702423</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6359097</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120308223</v>
+      </c>
+      <c r="B94" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>702425</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6359055</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120308226</v>
+      </c>
+      <c r="B95" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Hemse Ocksarve 2:1 (exklav i Lojsta), Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>702431</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6359070</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134682378</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>702259</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6359049</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>134682383</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Linde Rangsarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>702255</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6359034</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>104469397</v>
+      </c>
+      <c r="B98" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>702326</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6358917</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120419637</v>
+      </c>
+      <c r="B99" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>702224</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6358856</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120645042</v>
+      </c>
+      <c r="B100" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Graunvik, Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>702169</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6358801</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120645058</v>
+      </c>
+      <c r="B101" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Väster om Kvie källmyrs naturreservat, Graunvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>702279</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6358899</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>16869288</v>
+      </c>
+      <c r="B102" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Linde Myrungs 1:15/Linde Rangsarve 1:2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>702340</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6358873</v>
+      </c>
+      <c r="S102" t="n">
+        <v>20</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>104469395</v>
+      </c>
+      <c r="B103" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>702339</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6358948</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>104469399</v>
+      </c>
+      <c r="B104" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lojsta, Graunvik, 700 m SV Kvie Källmyrs NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>702283</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6358889</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Talldominerad kalkbarrskog på fuktig till frisk mark</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Michael Krikorev, Helena Björnström, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120419628</v>
+      </c>
+      <c r="B105" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Granuvik, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>702321</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6359134</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -6612,7 +6612,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -6719,7 +6719,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -6826,7 +6826,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -6933,7 +6933,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -7040,7 +7040,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -7152,7 +7152,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -7264,7 +7264,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -7376,7 +7376,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
@@ -7483,7 +7483,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -7590,7 +7590,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -7697,7 +7697,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -7804,7 +7804,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
@@ -7911,7 +7911,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -8018,7 +8018,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -8125,7 +8125,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -8232,7 +8232,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -8344,7 +8344,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Linde Rangsarve 922, Gtl</t>
+          <t>Linde Rangsarve, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">

--- a/artfynd/A 922-2023 artfynd.xlsx
+++ b/artfynd/A 922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120644809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120644847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120644959</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419634</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120644922</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419631</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120644805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97389934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340635</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340681</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869289</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419638</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120644923</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869292</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645098</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2362,6 +2447,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419635</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2468,6 +2558,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869291</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1339313</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2675,6 +2775,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104469398</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2774,6 +2879,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419627</t>
         </is>
       </c>
     </row>
@@ -2886,6 +2996,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104469396</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308386</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3104,6 +3224,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14846064</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3216,6 +3341,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682296</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682301</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3435,6 +3570,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682306</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3542,6 +3682,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682309</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3654,6 +3799,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682312</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3766,6 +3916,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682316</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3878,6 +4033,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682318</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3985,6 +4145,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682325</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4092,6 +4257,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682328</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4204,6 +4374,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682330</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4311,6 +4486,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682335</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4418,6 +4598,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682340</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4525,6 +4710,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682342</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4632,6 +4822,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682347</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4739,6 +4934,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682349</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4846,6 +5046,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682353</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4953,6 +5158,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682355</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5060,6 +5270,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682360</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5167,6 +5382,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682362</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5274,6 +5494,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682364</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5381,6 +5606,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682370</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5488,6 +5718,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682373</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5595,6 +5830,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682375</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5702,6 +5942,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682379</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5814,6 +6059,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682380</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5921,6 +6171,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682384</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6033,6 +6288,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682386</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6145,6 +6405,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682387</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6252,6 +6517,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682389</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6364,6 +6634,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682390</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6471,6 +6746,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682391</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6578,6 +6858,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682394</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6685,6 +6970,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685337</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6792,6 +7082,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685339</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6899,6 +7194,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685341</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7006,6 +7306,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685342</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7118,6 +7423,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685343</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7230,6 +7540,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685344</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7342,6 +7657,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685345</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7449,6 +7769,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685349</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7556,6 +7881,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685351</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7663,6 +7993,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685355</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7770,6 +8105,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685356</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7877,6 +8217,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685357</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7984,6 +8329,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685358</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8091,6 +8441,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685359</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8198,6 +8553,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685360</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8310,6 +8670,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685361</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8422,6 +8787,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685362</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8533,6 +8903,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14846063</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8644,6 +9019,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308191</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8755,6 +9135,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308199</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8866,6 +9251,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308202</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8977,6 +9367,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308206</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9074,6 +9469,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97389933</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9185,6 +9585,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308178</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9296,6 +9701,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308180</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9398,6 +9808,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308166</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9500,6 +9915,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308184</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9602,6 +10022,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308186</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9704,6 +10129,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308189</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9806,6 +10236,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308195</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9908,6 +10343,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308197</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10010,6 +10450,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308200</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10121,6 +10566,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308207</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10232,6 +10682,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308211</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10334,6 +10789,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308216</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10445,6 +10905,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308220</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10556,6 +11021,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308223</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10667,6 +11137,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308226</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10774,6 +11249,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682378</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10881,6 +11361,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682383</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10991,6 +11476,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104469397</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11092,6 +11582,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419637</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11199,6 +11694,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645042</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11296,6 +11796,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645058</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11402,6 +11907,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869288</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11512,6 +12022,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104469395</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11622,6 +12137,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104469399</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11723,8 +12243,119 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>